--- a/modelo-logradouro.xlsx
+++ b/modelo-logradouro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CONTROLE DE QUALIDADE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B5E37DB2-B6CC-42E8-8A1D-5ACC1C299486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5DC8F0-EC72-4E18-B052-F0DF1C5F122C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -226,7 +226,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -281,6 +281,68 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -409,15 +471,6 @@
     <xf numFmtId="164" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="9" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -427,13 +480,22 @@
     <xf numFmtId="49" fontId="9" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -474,55 +536,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>666461</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>723790</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagem 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="19050" y="228600"/>
-          <a:ext cx="2314286" cy="685690"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -827,19 +840,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36"/>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="42" t="s">
+      <c r="A1" s="39" t="s">
         <v>7</v>
       </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
       <c r="C2" s="43"/>
       <c r="D2" s="43"/>
       <c r="E2" s="43"/>
@@ -847,14 +860,14 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="40"/>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="41"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="38"/>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1024,16 +1037,14 @@
       <c r="F22" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:F1"/>
+  <mergeCells count="2">
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="A1:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:E11">
     <cfRule type="duplicateValues" dxfId="0" priority="6" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.23622047244094491" right="0.51181102362204722" top="0.28999999999999998" bottom="0.19" header="0.19" footer="0.12"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>